--- a/02_Inputs/Translation/es.xlsx
+++ b/02_Inputs/Translation/es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/SEH/Sustainable Energy Academy/Academy_Pipeline/dsc-energy-academy-pipeline/02_Inputs/Translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C844DD2E-6E9C-8549-9022-7DBDC44C6708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBA1318-765A-0E45-8197-CD08F8666958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="3180" windowWidth="26040" windowHeight="14640" xr2:uid="{3C3ACF3F-938D-D142-86CB-11FB46888555}"/>
+    <workbookView xWindow="34880" yWindow="1380" windowWidth="26040" windowHeight="14640" xr2:uid="{3C3ACF3F-938D-D142-86CB-11FB46888555}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>original</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>casita</t>
+  </si>
+  <si>
+    <t>english</t>
+  </si>
+  <si>
+    <t>little house</t>
   </si>
 </sst>
 </file>
@@ -419,22 +425,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCBF35BD-9B13-DE41-9FFD-5D5745D0C18A}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
     </row>
